--- a/MEX_WB_timeseries.xlsx
+++ b/MEX_WB_timeseries.xlsx
@@ -14,21 +14,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank liquid reserves to bank assets (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Debt (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
+  <si>
+    <t>External debt stocks (% of GNI)</t>
+  </si>
+  <si>
+    <t>External debt stocks (current US$)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +485,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AL26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,454 +507,2656 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:38">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="E2">
+        <v>-0.07386030256748199</v>
+      </c>
+      <c r="F2">
+        <v>-2.52707170138346</v>
+      </c>
+      <c r="G2">
+        <v>18.1918633340197</v>
+      </c>
+      <c r="H2">
+        <v>14.3477809518427</v>
+      </c>
+      <c r="I2">
+        <v>24.2311734681303</v>
+      </c>
+      <c r="J2">
+        <v>24.5014645772111</v>
+      </c>
+      <c r="K2">
+        <v>178113615414.8</v>
+      </c>
+      <c r="L2">
         <v>5.02928399378261</v>
       </c>
-      <c r="C2">
+      <c r="M2">
+        <v>11704.3811052518</v>
+      </c>
+      <c r="N2">
+        <v>7524.0271380091</v>
+      </c>
+      <c r="O2">
+        <v>3.42140514214798</v>
+      </c>
+      <c r="P2">
+        <v>53.4</v>
+      </c>
+      <c r="Q2">
+        <v>0.276181936264038</v>
+      </c>
+      <c r="R2">
+        <v>9.037016014457979</v>
+      </c>
+      <c r="S2">
+        <v>12.0964929315521</v>
+      </c>
+      <c r="T2">
+        <v>11.5528823713743</v>
+      </c>
+      <c r="U2">
+        <v>25.6792357191195</v>
+      </c>
+      <c r="V2">
         <v>9.491561494354031</v>
       </c>
-      <c r="D2">
+      <c r="W2">
         <v>13.3324614762896</v>
       </c>
-      <c r="E2">
+      <c r="X2">
+        <v>72.562</v>
+      </c>
+      <c r="Y2">
+        <v>0.446047820449759</v>
+      </c>
+      <c r="Z2">
+        <v>-0.91702482458329</v>
+      </c>
+      <c r="AA2">
+        <v>-0.200209870934486</v>
+      </c>
+      <c r="AB2">
+        <v>98625552</v>
+      </c>
+      <c r="AC2">
+        <v>16.3</v>
+      </c>
+      <c r="AD2">
+        <v>0.220494195818901</v>
+      </c>
+      <c r="AE2">
+        <v>-0.42650955915451</v>
+      </c>
+      <c r="AF2">
         <v>9.132295412501669</v>
       </c>
-      <c r="F2">
+      <c r="AG2">
+        <v>35577279053.6649</v>
+      </c>
+      <c r="AH2">
+        <v>2.01762486355417</v>
+      </c>
+      <c r="AI2">
+        <v>49.9104091872497</v>
+      </c>
+      <c r="AJ2">
         <v>2.646</v>
       </c>
+      <c r="AK2">
+        <v>74.72199999999999</v>
+      </c>
+      <c r="AL2">
+        <v>0.258450001478195</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:38">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>12.9746942749413</v>
+      </c>
+      <c r="F3">
+        <v>-2.23003398954777</v>
+      </c>
+      <c r="H3">
+        <v>12.240977233378</v>
+      </c>
+      <c r="I3">
+        <v>21.5412102050357</v>
+      </c>
+      <c r="J3">
+        <v>25.9016210708753</v>
+      </c>
+      <c r="K3">
+        <v>202572533842.5</v>
+      </c>
+      <c r="L3">
         <v>-0.450845253215945</v>
       </c>
-      <c r="C3">
+      <c r="M3">
+        <v>11738.7259429144</v>
+      </c>
+      <c r="N3">
+        <v>7952.76479510706</v>
+      </c>
+      <c r="O3">
+        <v>-1.9162965888934</v>
+      </c>
+      <c r="R3">
+        <v>9.35531059790458</v>
+      </c>
+      <c r="U3">
+        <v>23.1988988072816</v>
+      </c>
+      <c r="V3">
         <v>6.36773806235037</v>
       </c>
-      <c r="F3">
+      <c r="X3">
+        <v>72.91200000000001</v>
+      </c>
+      <c r="Y3">
+        <v>0.442657003961602</v>
+      </c>
+      <c r="AB3">
+        <v>100099099</v>
+      </c>
+      <c r="AG3">
+        <v>44804667773.015</v>
+      </c>
+      <c r="AH3">
+        <v>2.63689971681986</v>
+      </c>
+      <c r="AI3">
+        <v>44.7401090123173</v>
+      </c>
+      <c r="AJ3">
         <v>2.627</v>
       </c>
+      <c r="AK3">
+        <v>75.045</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:38">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="C4">
+        <v>17.6356339348153</v>
+      </c>
+      <c r="E4">
+        <v>-0.250572264194489</v>
+      </c>
+      <c r="F4">
+        <v>-1.52936520808688</v>
+      </c>
+      <c r="H4">
+        <v>14.1782625366026</v>
+      </c>
+      <c r="I4">
+        <v>21.8517619236376</v>
+      </c>
+      <c r="J4">
+        <v>24.1586324811681</v>
+      </c>
+      <c r="K4">
+        <v>193461604962.7</v>
+      </c>
+      <c r="L4">
         <v>-0.236588001922641</v>
       </c>
-      <c r="C4">
+      <c r="M4">
+        <v>11761.8865901666</v>
+      </c>
+      <c r="N4">
+        <v>7983.03398381759</v>
+      </c>
+      <c r="O4">
+        <v>-1.66063053524651</v>
+      </c>
+      <c r="P4">
+        <v>50.6</v>
+      </c>
+      <c r="Q4">
+        <v>0.218386545777321</v>
+      </c>
+      <c r="R4">
+        <v>9.838122457984451</v>
+      </c>
+      <c r="U4">
+        <v>23.3580673360145</v>
+      </c>
+      <c r="V4">
         <v>5.03072733151295</v>
       </c>
-      <c r="F4">
+      <c r="X4">
+        <v>73.10599999999999</v>
+      </c>
+      <c r="Y4">
+        <v>0.421606002464969</v>
+      </c>
+      <c r="AA4">
+        <v>-0.0583082623779774</v>
+      </c>
+      <c r="AB4">
+        <v>101548624</v>
+      </c>
+      <c r="AC4">
+        <v>12.8</v>
+      </c>
+      <c r="AD4">
+        <v>0.438464432954788</v>
+      </c>
+      <c r="AE4">
+        <v>-0.349208414554596</v>
+      </c>
+      <c r="AG4">
+        <v>50671452144.9585</v>
+      </c>
+      <c r="AH4">
+        <v>2.98006982310122</v>
+      </c>
+      <c r="AI4">
+        <v>45.209829259652</v>
+      </c>
+      <c r="AJ4">
         <v>3.003</v>
       </c>
+      <c r="AK4">
+        <v>75.36499999999999</v>
+      </c>
+      <c r="AL4">
+        <v>0.346043467521667</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:38">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>19.0307121056459</v>
+      </c>
+      <c r="E5">
+        <v>-0.2415871322155</v>
+      </c>
+      <c r="F5">
+        <v>-0.526761129534337</v>
+      </c>
+      <c r="H5">
+        <v>14.6412754593329</v>
+      </c>
+      <c r="I5">
+        <v>23.6555935033272</v>
+      </c>
+      <c r="J5">
+        <v>26.3218083549679</v>
+      </c>
+      <c r="K5">
+        <v>199260698324.5</v>
+      </c>
+      <c r="L5">
         <v>1.18554486709559</v>
       </c>
-      <c r="C5">
+      <c r="M5">
+        <v>12066.1601262353</v>
+      </c>
+      <c r="N5">
+        <v>7434.07465031562</v>
+      </c>
+      <c r="O5">
+        <v>-0.219450145073267</v>
+      </c>
+      <c r="Q5">
+        <v>0.131819322705269</v>
+      </c>
+      <c r="R5">
+        <v>10.4980403656953</v>
+      </c>
+      <c r="U5">
+        <v>25.0448233657183</v>
+      </c>
+      <c r="V5">
         <v>4.54690012118718</v>
       </c>
-      <c r="F5">
+      <c r="X5">
+        <v>73.30800000000001</v>
+      </c>
+      <c r="Y5">
+        <v>0.405916546649963</v>
+      </c>
+      <c r="AA5">
+        <v>-0.11687808483839</v>
+      </c>
+      <c r="AB5">
+        <v>102978515</v>
+      </c>
+      <c r="AD5">
+        <v>0.335378050804138</v>
+      </c>
+      <c r="AE5">
+        <v>-0.377902716398239</v>
+      </c>
+      <c r="AG5">
+        <v>59026700311.4513</v>
+      </c>
+      <c r="AH5">
+        <v>3.44046588174088</v>
+      </c>
+      <c r="AI5">
+        <v>48.7004168690455</v>
+      </c>
+      <c r="AJ5">
         <v>3.455</v>
       </c>
+      <c r="AK5">
+        <v>75.682</v>
+      </c>
+      <c r="AL5">
+        <v>0.346937119960785</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:38">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>18.5749893172144</v>
+      </c>
+      <c r="E6">
+        <v>-0.389334857463837</v>
+      </c>
+      <c r="F6">
+        <v>-0.464775659455355</v>
+      </c>
+      <c r="H6">
+        <v>14.1054932641584</v>
+      </c>
+      <c r="I6">
+        <v>25.1033560080055</v>
+      </c>
+      <c r="J6">
+        <v>25.8629949355891</v>
+      </c>
+      <c r="K6">
+        <v>210040194664.4</v>
+      </c>
+      <c r="L6">
         <v>3.56544102622887</v>
       </c>
-      <c r="C6">
+      <c r="M6">
+        <v>12657.8156092307</v>
+      </c>
+      <c r="N6">
+        <v>7849.66759649565</v>
+      </c>
+      <c r="O6">
+        <v>2.16106231298699</v>
+      </c>
+      <c r="P6">
+        <v>50.3</v>
+      </c>
+      <c r="Q6">
+        <v>0.07583381235599521</v>
+      </c>
+      <c r="R6">
+        <v>10.0161818460585</v>
+      </c>
+      <c r="U6">
+        <v>26.9372640255577</v>
+      </c>
+      <c r="V6">
         <v>4.68840884843143</v>
       </c>
-      <c r="F6">
+      <c r="X6">
+        <v>73.432</v>
+      </c>
+      <c r="Y6">
+        <v>0.364898722678153</v>
+      </c>
+      <c r="AA6">
+        <v>-0.214082449674606</v>
+      </c>
+      <c r="AB6">
+        <v>104394131</v>
+      </c>
+      <c r="AC6">
+        <v>11</v>
+      </c>
+      <c r="AD6">
+        <v>0.410247594118118</v>
+      </c>
+      <c r="AE6">
+        <v>-0.409910470247269</v>
+      </c>
+      <c r="AG6">
+        <v>64201699862.8694</v>
+      </c>
+      <c r="AH6">
+        <v>3.28782723404344</v>
+      </c>
+      <c r="AI6">
+        <v>52.0406200335632</v>
+      </c>
+      <c r="AJ6">
         <v>3.937</v>
       </c>
+      <c r="AK6">
+        <v>75.997</v>
+      </c>
+      <c r="AL6">
+        <v>0.319827616214752</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:38">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
+        <v>7.67386956333956</v>
+      </c>
+      <c r="C7">
+        <v>20.450395147705</v>
+      </c>
+      <c r="D7">
+        <v>1.81638248738848</v>
+      </c>
+      <c r="E7">
+        <v>-0.344179540872574</v>
+      </c>
+      <c r="F7">
+        <v>-0.623534401583354</v>
+      </c>
+      <c r="H7">
+        <v>15.3135908131833</v>
+      </c>
+      <c r="I7">
+        <v>25.4870738285114</v>
+      </c>
+      <c r="J7">
+        <v>24.1351947655204</v>
+      </c>
+      <c r="K7">
+        <v>218225512951.4</v>
+      </c>
+      <c r="L7">
         <v>2.11324711473297</v>
       </c>
-      <c r="C7">
+      <c r="M7">
+        <v>13260.2388186669</v>
+      </c>
+      <c r="N7">
+        <v>8671.75891885163</v>
+      </c>
+      <c r="O7">
+        <v>0.745413240991311</v>
+      </c>
+      <c r="P7">
+        <v>50.9</v>
+      </c>
+      <c r="Q7">
+        <v>0.0314169824123383</v>
+      </c>
+      <c r="R7">
+        <v>10.0762299851121</v>
+      </c>
+      <c r="U7">
+        <v>27.0755708232772</v>
+      </c>
+      <c r="V7">
         <v>3.98805714597437</v>
       </c>
-      <c r="F7">
+      <c r="X7">
+        <v>73.627</v>
+      </c>
+      <c r="Y7">
+        <v>0.355958931501411</v>
+      </c>
+      <c r="AA7">
+        <v>-0.445820868015289</v>
+      </c>
+      <c r="AB7">
+        <v>105811504</v>
+      </c>
+      <c r="AC7">
+        <v>11.7</v>
+      </c>
+      <c r="AD7">
+        <v>0.160981357097626</v>
+      </c>
+      <c r="AE7">
+        <v>-0.382989525794983</v>
+      </c>
+      <c r="AG7">
+        <v>74109703346.0659</v>
+      </c>
+      <c r="AH7">
+        <v>3.31288171093641</v>
+      </c>
+      <c r="AI7">
+        <v>52.5626446517886</v>
+      </c>
+      <c r="AJ7">
         <v>3.558</v>
       </c>
+      <c r="AK7">
+        <v>76.30800000000001</v>
+      </c>
+      <c r="AL7">
+        <v>0.198065519332886</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:38">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
+        <v>8.75421645126092</v>
+      </c>
+      <c r="C8">
+        <v>15.0088312744943</v>
+      </c>
+      <c r="D8">
+        <v>1.9944212361405</v>
+      </c>
+      <c r="E8">
+        <v>-0.325125187635422</v>
+      </c>
+      <c r="F8">
+        <v>-0.316555541136009</v>
+      </c>
+      <c r="H8">
+        <v>18.3518916727969</v>
+      </c>
+      <c r="I8">
+        <v>26.5547481705759</v>
+      </c>
+      <c r="J8">
+        <v>22.0731084517312</v>
+      </c>
+      <c r="K8">
+        <v>221829065156.6</v>
+      </c>
+      <c r="L8">
         <v>4.80501351664901</v>
       </c>
-      <c r="C8">
+      <c r="M8">
+        <v>14541.6716295608</v>
+      </c>
+      <c r="N8">
+        <v>9512.63575346699</v>
+      </c>
+      <c r="O8">
+        <v>3.39577676474912</v>
+      </c>
+      <c r="P8">
+        <v>49.7</v>
+      </c>
+      <c r="Q8">
+        <v>0.0504711605608463</v>
+      </c>
+      <c r="R8">
+        <v>9.89214269664029</v>
+      </c>
+      <c r="U8">
+        <v>27.927367918041</v>
+      </c>
+      <c r="V8">
         <v>3.62946762439132</v>
       </c>
-      <c r="F8">
+      <c r="X8">
+        <v>73.746</v>
+      </c>
+      <c r="Y8">
+        <v>0.311171936508264</v>
+      </c>
+      <c r="AA8">
+        <v>-0.636888444423676</v>
+      </c>
+      <c r="AB8">
+        <v>107253666</v>
+      </c>
+      <c r="AC8">
+        <v>9</v>
+      </c>
+      <c r="AD8">
+        <v>0.346685439348221</v>
+      </c>
+      <c r="AE8">
+        <v>-0.472546279430389</v>
+      </c>
+      <c r="AG8">
+        <v>76329367204.2543</v>
+      </c>
+      <c r="AH8">
+        <v>2.96677953801298</v>
+      </c>
+      <c r="AI8">
+        <v>54.4821160886169</v>
+      </c>
+      <c r="AJ8">
         <v>3.566</v>
       </c>
+      <c r="AK8">
+        <v>76.616</v>
+      </c>
+      <c r="AL8">
+        <v>0.150474414229393</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:38">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
+        <v>9.206018801468741</v>
+      </c>
+      <c r="C9">
+        <v>11.1097322808628</v>
+      </c>
+      <c r="D9">
+        <v>2.5413127799359</v>
+      </c>
+      <c r="E9">
+        <v>-0.341457366943359</v>
+      </c>
+      <c r="F9">
+        <v>-0.844640815368309</v>
+      </c>
+      <c r="H9">
+        <v>20.4394698066311</v>
+      </c>
+      <c r="I9">
+        <v>26.7810613301488</v>
+      </c>
+      <c r="J9">
+        <v>23.1063024242461</v>
+      </c>
+      <c r="K9">
+        <v>250650606340.3</v>
+      </c>
+      <c r="L9">
         <v>2.0778639395329</v>
       </c>
-      <c r="C9">
+      <c r="M9">
+        <v>15031.86195805</v>
+      </c>
+      <c r="N9">
+        <v>10134.3327129706</v>
+      </c>
+      <c r="O9">
+        <v>0.650788705758472</v>
+      </c>
+      <c r="Q9">
+        <v>0.136410132050514</v>
+      </c>
+      <c r="R9">
+        <v>9.947892834536299</v>
+      </c>
+      <c r="U9">
+        <v>28.477463068888</v>
+      </c>
+      <c r="V9">
         <v>3.96684905458234</v>
       </c>
-      <c r="F9">
+      <c r="X9">
+        <v>73.79600000000001</v>
+      </c>
+      <c r="Y9">
+        <v>0.401163917952381</v>
+      </c>
+      <c r="AA9">
+        <v>-0.729851603507996</v>
+      </c>
+      <c r="AB9">
+        <v>108774360</v>
+      </c>
+      <c r="AD9">
+        <v>0.368228048086166</v>
+      </c>
+      <c r="AE9">
+        <v>-0.542932212352753</v>
+      </c>
+      <c r="AG9">
+        <v>87208175923.3125</v>
+      </c>
+      <c r="AH9">
+        <v>3.06932316704467</v>
+      </c>
+      <c r="AI9">
+        <v>55.2585243990368</v>
+      </c>
+      <c r="AJ9">
         <v>3.628</v>
       </c>
+      <c r="AK9">
+        <v>76.92</v>
+      </c>
+      <c r="AL9">
+        <v>0.121899016201496</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:38">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>9.267039601403891</v>
+      </c>
+      <c r="C10">
+        <v>12.8671985732358</v>
+      </c>
+      <c r="D10">
+        <v>3.20802543521284</v>
+      </c>
+      <c r="E10">
+        <v>-0.309849888086319</v>
+      </c>
+      <c r="F10">
+        <v>-1.40680860932702</v>
+      </c>
+      <c r="H10">
+        <v>19.7553753175775</v>
+      </c>
+      <c r="I10">
+        <v>27.02006122825</v>
+      </c>
+      <c r="J10">
+        <v>21.6625866213129</v>
+      </c>
+      <c r="K10">
+        <v>248240107870.4</v>
+      </c>
+      <c r="L10">
         <v>0.943331872912935</v>
       </c>
-      <c r="C10">
+      <c r="M10">
+        <v>15680.5761933269</v>
+      </c>
+      <c r="N10">
+        <v>10523.7685427665</v>
+      </c>
+      <c r="O10">
+        <v>-0.519889915451088</v>
+      </c>
+      <c r="P10">
+        <v>50.8</v>
+      </c>
+      <c r="Q10">
+        <v>0.16068996489048</v>
+      </c>
+      <c r="R10">
+        <v>10.2592374986528</v>
+      </c>
+      <c r="T10">
+        <v>19.7297455421069</v>
+      </c>
+      <c r="U10">
+        <v>29.3452206449273</v>
+      </c>
+      <c r="V10">
         <v>5.12498274575896</v>
       </c>
-      <c r="E10">
+      <c r="X10">
+        <v>73.69499999999999</v>
+      </c>
+      <c r="Y10">
+        <v>0.390513227488772</v>
+      </c>
+      <c r="AA10">
+        <v>-0.804012358188629</v>
+      </c>
+      <c r="AB10">
+        <v>110374288</v>
+      </c>
+      <c r="AC10">
+        <v>10.1</v>
+      </c>
+      <c r="AD10">
+        <v>0.312569350004196</v>
+      </c>
+      <c r="AE10">
+        <v>-0.689283549785614</v>
+      </c>
+      <c r="AF10">
         <v>9.5787715278782</v>
       </c>
-      <c r="F10">
+      <c r="AG10">
+        <v>95299838182.8513</v>
+      </c>
+      <c r="AH10">
+        <v>3.10571376172191</v>
+      </c>
+      <c r="AI10">
+        <v>56.3652818731773</v>
+      </c>
+      <c r="AJ10">
         <v>3.874</v>
       </c>
+      <c r="AK10">
+        <v>77.22199999999999</v>
+      </c>
+      <c r="AL10">
+        <v>0.134927570819855</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:38">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
+        <v>9.88565799396453</v>
+      </c>
+      <c r="C11">
+        <v>11.5516452480529</v>
+      </c>
+      <c r="D11">
+        <v>3.06903578149087</v>
+      </c>
+      <c r="E11">
+        <v>-0.365960121154785</v>
+      </c>
+      <c r="F11">
+        <v>-0.750928571008078</v>
+      </c>
+      <c r="H11">
+        <v>21.6119225648182</v>
+      </c>
+      <c r="I11">
+        <v>26.5132697232887</v>
+      </c>
+      <c r="J11">
+        <v>26.9674757913441</v>
+      </c>
+      <c r="K11">
+        <v>250545865969.3</v>
+      </c>
+      <c r="L11">
         <v>-6.29525056697287</v>
       </c>
-      <c r="C11">
+      <c r="M11">
+        <v>15192.6241502056</v>
+      </c>
+      <c r="N11">
+        <v>8423.56933214711</v>
+      </c>
+      <c r="O11">
+        <v>-7.65517174021555</v>
+      </c>
+      <c r="Q11">
+        <v>0.141515776515007</v>
+      </c>
+      <c r="R11">
+        <v>11.3834438576777</v>
+      </c>
+      <c r="S11">
+        <v>20.5779680774514</v>
+      </c>
+      <c r="T11">
+        <v>16.8831719121647</v>
+      </c>
+      <c r="U11">
+        <v>28.0784724080616</v>
+      </c>
+      <c r="V11">
         <v>5.29735584228857</v>
       </c>
-      <c r="D11">
+      <c r="W11">
         <v>11.4551176989766</v>
       </c>
-      <c r="E11">
+      <c r="X11">
+        <v>73.628</v>
+      </c>
+      <c r="Y11">
+        <v>0.501556274697719</v>
+      </c>
+      <c r="Z11">
+        <v>-4.30408718038352</v>
+      </c>
+      <c r="AA11">
+        <v>-0.686627805233002</v>
+      </c>
+      <c r="AB11">
+        <v>111999721</v>
+      </c>
+      <c r="AD11">
+        <v>0.177682906389236</v>
+      </c>
+      <c r="AE11">
+        <v>-0.56286883354187</v>
+      </c>
+      <c r="AF11">
         <v>9.234604861369091</v>
       </c>
-      <c r="F11">
+      <c r="AG11">
+        <v>99888815494.34531</v>
+      </c>
+      <c r="AH11">
+        <v>4.18740932590072</v>
+      </c>
+      <c r="AI11">
+        <v>54.5917421313503</v>
+      </c>
+      <c r="AJ11">
         <v>5.356</v>
       </c>
+      <c r="AK11">
+        <v>77.52</v>
+      </c>
+      <c r="AL11">
+        <v>0.200032845139503</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:38">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
+        <v>9.635583281951121</v>
+      </c>
+      <c r="C12">
+        <v>9.448941172939691</v>
+      </c>
+      <c r="D12">
+        <v>2.32838597424659</v>
+      </c>
+      <c r="E12">
+        <v>-0.439748138189316</v>
+      </c>
+      <c r="F12">
+        <v>-0.339592498699558</v>
+      </c>
+      <c r="H12">
+        <v>22.3237750289598</v>
+      </c>
+      <c r="I12">
+        <v>29.0174601196541</v>
+      </c>
+      <c r="J12">
+        <v>28.5700387892859</v>
+      </c>
+      <c r="K12">
+        <v>312338399290.8</v>
+      </c>
+      <c r="L12">
         <v>4.97133457799899</v>
       </c>
-      <c r="C12">
+      <c r="M12">
+        <v>15908.8603191799</v>
+      </c>
+      <c r="N12">
+        <v>9728.800782377821</v>
+      </c>
+      <c r="O12">
+        <v>3.47084286921813</v>
+      </c>
+      <c r="P12">
+        <v>47.7</v>
+      </c>
+      <c r="Q12">
+        <v>0.09629138559103009</v>
+      </c>
+      <c r="R12">
+        <v>11.2739649265619</v>
+      </c>
+      <c r="S12">
+        <v>20.4815497561358</v>
+      </c>
+      <c r="T12">
+        <v>17.2660921788065</v>
+      </c>
+      <c r="U12">
+        <v>30.255924418218</v>
+      </c>
+      <c r="V12">
         <v>4.15672722680173</v>
       </c>
-      <c r="D12">
+      <c r="W12">
         <v>10.9808598734044</v>
       </c>
-      <c r="E12">
+      <c r="X12">
+        <v>73.718</v>
+      </c>
+      <c r="Y12">
+        <v>0.433229899207479</v>
+      </c>
+      <c r="Z12">
+        <v>-3.80570262536555</v>
+      </c>
+      <c r="AA12">
+        <v>-0.726463437080383</v>
+      </c>
+      <c r="AB12">
+        <v>113623895</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>0.156337782740593</v>
+      </c>
+      <c r="AE12">
+        <v>-0.552031338214874</v>
+      </c>
+      <c r="AF12">
         <v>9.67531745462168</v>
       </c>
-      <c r="F12">
+      <c r="AG12">
+        <v>120584016515.123</v>
+      </c>
+      <c r="AH12">
+        <v>4.05364499570365</v>
+      </c>
+      <c r="AI12">
+        <v>59.2733845378721</v>
+      </c>
+      <c r="AJ12">
         <v>5.303</v>
       </c>
+      <c r="AK12">
+        <v>77.815</v>
+      </c>
+      <c r="AL12">
+        <v>0.178501576185226</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:38">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>8.89157267044717</v>
+      </c>
+      <c r="C13">
+        <v>8.05120984600603</v>
+      </c>
+      <c r="D13">
+        <v>2.44685147061432</v>
+      </c>
+      <c r="E13">
+        <v>-0.474737763404846</v>
+      </c>
+      <c r="F13">
+        <v>-0.857892612206586</v>
+      </c>
+      <c r="H13">
+        <v>23.5848328356452</v>
+      </c>
+      <c r="I13">
+        <v>30.442966223499</v>
+      </c>
+      <c r="J13">
+        <v>29.0507246312065</v>
+      </c>
+      <c r="K13">
+        <v>351694706992.3</v>
+      </c>
+      <c r="L13">
         <v>3.44404506308874</v>
       </c>
-      <c r="C13">
+      <c r="M13">
+        <v>17266.8129129167</v>
+      </c>
+      <c r="N13">
+        <v>10664.4944046282</v>
+      </c>
+      <c r="O13">
+        <v>1.99026328307114</v>
+      </c>
+      <c r="Q13">
+        <v>0.25232720375061</v>
+      </c>
+      <c r="R13">
+        <v>11.3282462801955</v>
+      </c>
+      <c r="S13">
+        <v>20.8740737942661</v>
+      </c>
+      <c r="T13">
+        <v>18.169056268833</v>
+      </c>
+      <c r="U13">
+        <v>31.7194210448082</v>
+      </c>
+      <c r="V13">
         <v>3.40737824605738</v>
       </c>
-      <c r="D13">
+      <c r="W13">
         <v>10.1107158294559</v>
       </c>
-      <c r="E13">
+      <c r="X13">
+        <v>73.92100000000001</v>
+      </c>
+      <c r="Y13">
+        <v>0.447386994111846</v>
+      </c>
+      <c r="Z13">
+        <v>-3.41832172549317</v>
+      </c>
+      <c r="AA13">
+        <v>-0.667768597602844</v>
+      </c>
+      <c r="AB13">
+        <v>115243504</v>
+      </c>
+      <c r="AD13">
+        <v>0.184377461671829</v>
+      </c>
+      <c r="AE13">
+        <v>-0.549887716770172</v>
+      </c>
+      <c r="AF13">
         <v>9.61707214507843</v>
       </c>
-      <c r="F13">
+      <c r="AG13">
+        <v>149208113907.362</v>
+      </c>
+      <c r="AH13">
+        <v>4.27630853093349</v>
+      </c>
+      <c r="AI13">
+        <v>62.1623872683072</v>
+      </c>
+      <c r="AJ13">
         <v>5.175</v>
       </c>
+      <c r="AK13">
+        <v>78.111</v>
+      </c>
+      <c r="AL13">
+        <v>0.12169187515974</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:38">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>9.3523758332804</v>
+      </c>
+      <c r="C14">
+        <v>7.80002067710539</v>
+      </c>
+      <c r="D14">
+        <v>2.52922017747363</v>
+      </c>
+      <c r="E14">
+        <v>-0.484527587890625</v>
+      </c>
+      <c r="F14">
+        <v>-1.40984864767656</v>
+      </c>
+      <c r="H14">
+        <v>24.9270563840333</v>
+      </c>
+      <c r="I14">
+        <v>31.5394503952292</v>
+      </c>
+      <c r="J14">
+        <v>35.2377254876682</v>
+      </c>
+      <c r="K14">
+        <v>432987558051.4</v>
+      </c>
+      <c r="L14">
         <v>3.55321075512755</v>
       </c>
-      <c r="C14">
+      <c r="M14">
+        <v>18004.7935585757</v>
+      </c>
+      <c r="N14">
+        <v>10744.1335229686</v>
+      </c>
+      <c r="O14">
+        <v>2.1573182998269</v>
+      </c>
+      <c r="P14">
+        <v>49.6</v>
+      </c>
+      <c r="Q14">
+        <v>0.296199023723602</v>
+      </c>
+      <c r="R14">
+        <v>11.4486765382534</v>
+      </c>
+      <c r="S14">
+        <v>20.9324326043308</v>
+      </c>
+      <c r="T14">
+        <v>17.9381165867739</v>
+      </c>
+      <c r="U14">
+        <v>32.7184815025572</v>
+      </c>
+      <c r="V14">
         <v>4.11150981070296</v>
       </c>
-      <c r="D14">
+      <c r="W14">
         <v>10.2794816169468</v>
       </c>
-      <c r="E14">
+      <c r="X14">
+        <v>74.128</v>
+      </c>
+      <c r="Y14">
+        <v>0.455502058064299</v>
+      </c>
+      <c r="Z14">
+        <v>-3.65642642612901</v>
+      </c>
+      <c r="AA14">
+        <v>-0.662454187870026</v>
+      </c>
+      <c r="AB14">
+        <v>116818208</v>
+      </c>
+      <c r="AC14">
+        <v>7.3</v>
+      </c>
+      <c r="AD14">
+        <v>0.418743193149567</v>
+      </c>
+      <c r="AE14">
+        <v>-0.53518009185791</v>
+      </c>
+      <c r="AF14">
         <v>9.35241106361326</v>
       </c>
-      <c r="F14">
+      <c r="AG14">
+        <v>167075785316.037</v>
+      </c>
+      <c r="AH14">
+        <v>4.48471717639987</v>
+      </c>
+      <c r="AI14">
+        <v>64.25793189778641</v>
+      </c>
+      <c r="AJ14">
         <v>4.892</v>
       </c>
+      <c r="AK14">
+        <v>78.405</v>
+      </c>
+      <c r="AL14">
+        <v>0.112745344638824</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:38">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>8.959953321996039</v>
+      </c>
+      <c r="C15">
+        <v>7.21510770883665</v>
+      </c>
+      <c r="D15">
+        <v>3.36157018477857</v>
+      </c>
+      <c r="E15">
+        <v>-0.591898560523987</v>
+      </c>
+      <c r="F15">
+        <v>-2.39396960169622</v>
+      </c>
+      <c r="H15">
+        <v>27.8590593255176</v>
+      </c>
+      <c r="I15">
+        <v>30.7558005807208</v>
+      </c>
+      <c r="J15">
+        <v>39.1110646679957</v>
+      </c>
+      <c r="K15">
+        <v>504135518878.2</v>
+      </c>
+      <c r="L15">
         <v>0.852101550164704</v>
       </c>
-      <c r="C15">
+      <c r="M15">
+        <v>18170.2647920555</v>
+      </c>
+      <c r="N15">
+        <v>11216.800851866</v>
+      </c>
+      <c r="O15">
+        <v>-0.447810747405228</v>
+      </c>
+      <c r="Q15">
+        <v>0.302350997924805</v>
+      </c>
+      <c r="R15">
+        <v>11.7127320778729</v>
+      </c>
+      <c r="S15">
+        <v>20.6909750829168</v>
+      </c>
+      <c r="T15">
+        <v>18.0538404139904</v>
+      </c>
+      <c r="U15">
+        <v>31.9358741854644</v>
+      </c>
+      <c r="V15">
         <v>3.80639069747206</v>
       </c>
-      <c r="D15">
+      <c r="W15">
         <v>10.4733380731093</v>
       </c>
-      <c r="E15">
+      <c r="X15">
+        <v>74.289</v>
+      </c>
+      <c r="Y15">
+        <v>0.487642870144841</v>
+      </c>
+      <c r="Z15">
+        <v>-3.20354224005969</v>
+      </c>
+      <c r="AA15">
+        <v>-0.7142238020896911</v>
+      </c>
+      <c r="AB15">
+        <v>118343573</v>
+      </c>
+      <c r="AD15">
+        <v>0.418155193328857</v>
+      </c>
+      <c r="AE15">
+        <v>-0.549416422843933</v>
+      </c>
+      <c r="AF15">
         <v>9.88361012140901</v>
       </c>
-      <c r="F15">
+      <c r="AG15">
+        <v>180200033349.658</v>
+      </c>
+      <c r="AH15">
+        <v>4.5658776197185</v>
+      </c>
+      <c r="AI15">
+        <v>62.6916747661852</v>
+      </c>
+      <c r="AJ15">
         <v>4.921</v>
       </c>
+      <c r="AK15">
+        <v>78.699</v>
+      </c>
+      <c r="AL15">
+        <v>0.108349166810513</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:38">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>9.367252690159409</v>
+      </c>
+      <c r="C16">
+        <v>7.48781119720811</v>
+      </c>
+      <c r="D16">
+        <v>3.13402337702184</v>
+      </c>
+      <c r="E16">
+        <v>-0.84301882982254</v>
+      </c>
+      <c r="F16">
+        <v>-1.82131927642842</v>
+      </c>
+      <c r="H16">
+        <v>28.1836821045396</v>
+      </c>
+      <c r="I16">
+        <v>31.4629921965186</v>
+      </c>
+      <c r="J16">
+        <v>40.8517099412787</v>
+      </c>
+      <c r="K16">
+        <v>544166999708.7</v>
+      </c>
+      <c r="L16">
         <v>2.50376349862891</v>
       </c>
-      <c r="C16">
+      <c r="M16">
+        <v>18820.7991119337</v>
+      </c>
+      <c r="N16">
+        <v>11391.3773510244</v>
+      </c>
+      <c r="O16">
+        <v>1.27091420111299</v>
+      </c>
+      <c r="P16">
+        <v>48.9</v>
+      </c>
+      <c r="Q16">
+        <v>0.133970901370049</v>
+      </c>
+      <c r="R16">
+        <v>11.7538929130766</v>
+      </c>
+      <c r="S16">
+        <v>20.9971763620163</v>
+      </c>
+      <c r="T16">
+        <v>17.688599107291</v>
+      </c>
+      <c r="U16">
+        <v>32.6354168315349</v>
+      </c>
+      <c r="V16">
         <v>4.01861608078671</v>
       </c>
-      <c r="D16">
+      <c r="W16">
         <v>10.5750010754638</v>
       </c>
-      <c r="E16">
+      <c r="X16">
+        <v>74.404</v>
+      </c>
+      <c r="Y16">
+        <v>0.495321042296404</v>
+      </c>
+      <c r="Z16">
+        <v>-4.012501024096</v>
+      </c>
+      <c r="AA16">
+        <v>-0.853918790817261</v>
+      </c>
+      <c r="AB16">
+        <v>119784261</v>
+      </c>
+      <c r="AC16">
+        <v>7.2</v>
+      </c>
+      <c r="AD16">
+        <v>0.359438210725784</v>
+      </c>
+      <c r="AE16">
+        <v>-0.406688004732132</v>
+      </c>
+      <c r="AF16">
         <v>10.2428550424697</v>
       </c>
-      <c r="F16">
+      <c r="AG16">
+        <v>195681624545.922</v>
+      </c>
+      <c r="AH16">
+        <v>4.80529226012456</v>
+      </c>
+      <c r="AI16">
+        <v>64.0984090280535</v>
+      </c>
+      <c r="AJ16">
         <v>4.819</v>
       </c>
+      <c r="AK16">
+        <v>78.99299999999999</v>
+      </c>
+      <c r="AL16">
+        <v>0.000275321624940261</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:38">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>8.660075901296921</v>
+      </c>
+      <c r="C17">
+        <v>7.29576886808353</v>
+      </c>
+      <c r="D17">
+        <v>2.60441021807811</v>
+      </c>
+      <c r="E17">
+        <v>-0.8889673948287961</v>
+      </c>
+      <c r="F17">
+        <v>-2.59917628197071</v>
+      </c>
+      <c r="H17">
+        <v>30.8304978658063</v>
+      </c>
+      <c r="I17">
+        <v>34.1627726855471</v>
+      </c>
+      <c r="J17">
+        <v>45.4803129199232</v>
+      </c>
+      <c r="K17">
+        <v>538015200055.6</v>
+      </c>
+      <c r="L17">
         <v>2.70232344844723</v>
       </c>
-      <c r="C17">
+      <c r="M17">
+        <v>19075.3384711297</v>
+      </c>
+      <c r="N17">
+        <v>10021.2386124039</v>
+      </c>
+      <c r="O17">
+        <v>1.60971012855097</v>
+      </c>
+      <c r="Q17">
+        <v>0.117517560720444</v>
+      </c>
+      <c r="R17">
+        <v>11.901246125522</v>
+      </c>
+      <c r="S17">
+        <v>20.8689511506401</v>
+      </c>
+      <c r="T17">
+        <v>18.3681968705094</v>
+      </c>
+      <c r="U17">
+        <v>36.250201987055</v>
+      </c>
+      <c r="V17">
         <v>2.72064064964029</v>
       </c>
-      <c r="D17">
+      <c r="W17">
         <v>9.975376670814221</v>
       </c>
-      <c r="E17">
+      <c r="X17">
+        <v>74.431</v>
+      </c>
+      <c r="Y17">
+        <v>0.4507428192422</v>
+      </c>
+      <c r="Z17">
+        <v>-3.1188518817608</v>
+      </c>
+      <c r="AA17">
+        <v>-0.801780104637146</v>
+      </c>
+      <c r="AB17">
+        <v>121072306</v>
+      </c>
+      <c r="AD17">
+        <v>0.276325017213821</v>
+      </c>
+      <c r="AE17">
+        <v>-0.454765856266022</v>
+      </c>
+      <c r="AF17">
         <v>12.3459757808372</v>
       </c>
-      <c r="F17">
+      <c r="AG17">
+        <v>177596632552.624</v>
+      </c>
+      <c r="AH17">
+        <v>4.46007738307296</v>
+      </c>
+      <c r="AI17">
+        <v>70.4129746726021</v>
+      </c>
+      <c r="AJ17">
         <v>4.311</v>
       </c>
+      <c r="AK17">
+        <v>79.285</v>
+      </c>
+      <c r="AL17">
+        <v>-0.0753404349088669</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:38">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>8.384460794922679</v>
+      </c>
+      <c r="C18">
+        <v>7.03539022862881</v>
+      </c>
+      <c r="D18">
+        <v>2.14676314546594</v>
+      </c>
+      <c r="E18">
+        <v>-0.8506622910499571</v>
+      </c>
+      <c r="F18">
+        <v>-2.27311198277187</v>
+      </c>
+      <c r="H18">
+        <v>32.9508423866166</v>
+      </c>
+      <c r="I18">
+        <v>36.8156772514808</v>
+      </c>
+      <c r="J18">
+        <v>50.2965927131738</v>
+      </c>
+      <c r="K18">
+        <v>544792453300</v>
+      </c>
+      <c r="L18">
         <v>1.77249323400358</v>
       </c>
-      <c r="C18">
+      <c r="M18">
+        <v>20104.5839787472</v>
+      </c>
+      <c r="N18">
+        <v>9097.92397674769</v>
+      </c>
+      <c r="O18">
+        <v>0.790955211695035</v>
+      </c>
+      <c r="P18">
+        <v>46.9</v>
+      </c>
+      <c r="Q18">
+        <v>0.0276105776429176</v>
+      </c>
+      <c r="R18">
+        <v>11.5736804911904</v>
+      </c>
+      <c r="S18">
+        <v>20.3281994162596</v>
+      </c>
+      <c r="T18">
+        <v>19.1915888785393</v>
+      </c>
+      <c r="U18">
+        <v>38.8746261573743</v>
+      </c>
+      <c r="V18">
         <v>2.82170784747655</v>
       </c>
-      <c r="D18">
+      <c r="W18">
         <v>11.0357176857622</v>
       </c>
-      <c r="E18">
+      <c r="X18">
+        <v>74.376</v>
+      </c>
+      <c r="Y18">
+        <v>0.480046272445401</v>
+      </c>
+      <c r="Z18">
+        <v>-1.62118179871436</v>
+      </c>
+      <c r="AA18">
+        <v>-0.633718132972717</v>
+      </c>
+      <c r="AB18">
+        <v>122251351</v>
+      </c>
+      <c r="AC18">
+        <v>4.4</v>
+      </c>
+      <c r="AD18">
+        <v>0.199013441801071</v>
+      </c>
+      <c r="AE18">
+        <v>-0.579800665378571</v>
+      </c>
+      <c r="AF18">
         <v>13.1237856071941</v>
       </c>
-      <c r="F18">
+      <c r="AG18">
+        <v>177973637254.61</v>
+      </c>
+      <c r="AH18">
+        <v>4.54794007085504</v>
+      </c>
+      <c r="AI18">
+        <v>75.6903034088551</v>
+      </c>
+      <c r="AJ18">
         <v>3.853</v>
       </c>
+      <c r="AK18">
+        <v>79.577</v>
+      </c>
+      <c r="AL18">
+        <v>-0.0674507692456245</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:38">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>9.068666380920559</v>
+      </c>
+      <c r="C19">
+        <v>6.74277629948987</v>
+      </c>
+      <c r="D19">
+        <v>2.14605834181442</v>
+      </c>
+      <c r="E19">
+        <v>-0.952429533004761</v>
+      </c>
+      <c r="F19">
+        <v>-1.79746290774801</v>
+      </c>
+      <c r="H19">
+        <v>34.3431256723362</v>
+      </c>
+      <c r="I19">
+        <v>37.5140886198874</v>
+      </c>
+      <c r="J19">
+        <v>49.85860000761</v>
+      </c>
+      <c r="K19">
+        <v>578638429804.9</v>
+      </c>
+      <c r="L19">
         <v>1.87172854186539</v>
       </c>
-      <c r="C19">
+      <c r="M19">
+        <v>20488.7150800441</v>
+      </c>
+      <c r="N19">
+        <v>9649.27816772402</v>
+      </c>
+      <c r="O19">
+        <v>0.923425367204686</v>
+      </c>
+      <c r="Q19">
+        <v>-0.06530255079269411</v>
+      </c>
+      <c r="R19">
+        <v>11.2156675514112</v>
+      </c>
+      <c r="S19">
+        <v>19.8664920928197</v>
+      </c>
+      <c r="T19">
+        <v>19.4469058462512</v>
+      </c>
+      <c r="U19">
+        <v>39.438037420838</v>
+      </c>
+      <c r="V19">
         <v>6.04145724018993</v>
       </c>
-      <c r="D19">
+      <c r="W19">
         <v>13.3363748194504</v>
       </c>
-      <c r="E19">
+      <c r="X19">
+        <v>74.261</v>
+      </c>
+      <c r="Y19">
+        <v>0.424849159310516</v>
+      </c>
+      <c r="Z19">
+        <v>-0.845266946151578</v>
+      </c>
+      <c r="AA19">
+        <v>-0.806419789791107</v>
+      </c>
+      <c r="AB19">
+        <v>123400057</v>
+      </c>
+      <c r="AD19">
+        <v>0.182068794965744</v>
+      </c>
+      <c r="AE19">
+        <v>-0.5846487283706669</v>
+      </c>
+      <c r="AF19">
         <v>12.6874317280509</v>
       </c>
-      <c r="F19">
+      <c r="AG19">
+        <v>175469669183.544</v>
+      </c>
+      <c r="AH19">
+        <v>4.12120736692421</v>
+      </c>
+      <c r="AI19">
+        <v>76.9521260407254</v>
+      </c>
+      <c r="AJ19">
         <v>3.419</v>
       </c>
+      <c r="AK19">
+        <v>79.867</v>
+      </c>
+      <c r="AL19">
+        <v>-0.08905484527349471</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:38">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>9.13097972814708</v>
+      </c>
+      <c r="C20">
+        <v>7.13701781755115</v>
+      </c>
+      <c r="D20">
+        <v>2.1077378613675</v>
+      </c>
+      <c r="E20">
+        <v>-0.949163556098938</v>
+      </c>
+      <c r="F20">
+        <v>-2.0641407447465</v>
+      </c>
+      <c r="H20">
+        <v>33.6152178165449</v>
+      </c>
+      <c r="I20">
+        <v>39.043930445163</v>
+      </c>
+      <c r="J20">
+        <v>49.1902287792854</v>
+      </c>
+      <c r="K20">
+        <v>602000702060.1</v>
+      </c>
+      <c r="L20">
         <v>1.97208207701884</v>
       </c>
-      <c r="C20">
+      <c r="M20">
+        <v>20921.4775260265</v>
+      </c>
+      <c r="N20">
+        <v>10084.7937553679</v>
+      </c>
+      <c r="O20">
+        <v>1.01136619999065</v>
+      </c>
+      <c r="P20">
+        <v>46</v>
+      </c>
+      <c r="Q20">
+        <v>-0.292850613594055</v>
+      </c>
+      <c r="R20">
+        <v>11.2562967734042</v>
+      </c>
+      <c r="S20">
+        <v>19.8697097115272</v>
+      </c>
+      <c r="T20">
+        <v>18.3342427422463</v>
+      </c>
+      <c r="U20">
+        <v>41.1687312183701</v>
+      </c>
+      <c r="V20">
         <v>4.89935015356547</v>
       </c>
-      <c r="D20">
+      <c r="W20">
         <v>13.3810871048117</v>
       </c>
-      <c r="E20">
+      <c r="X20">
+        <v>74.301</v>
+      </c>
+      <c r="Y20">
+        <v>0.464611537244599</v>
+      </c>
+      <c r="Z20">
+        <v>-2.11318831534268</v>
+      </c>
+      <c r="AA20">
+        <v>-0.673847019672394</v>
+      </c>
+      <c r="AB20">
+        <v>124573711</v>
+      </c>
+      <c r="AC20">
+        <v>3.9</v>
+      </c>
+      <c r="AD20">
+        <v>0.0843754634261131</v>
+      </c>
+      <c r="AE20">
+        <v>-0.641221523284912</v>
+      </c>
+      <c r="AF20">
         <v>12.7121572984277</v>
       </c>
-      <c r="F20">
+      <c r="AG20">
+        <v>176390278595.584</v>
+      </c>
+      <c r="AH20">
+        <v>3.74611361421752</v>
+      </c>
+      <c r="AI20">
+        <v>80.2126616635331</v>
+      </c>
+      <c r="AJ20">
         <v>3.275</v>
       </c>
+      <c r="AK20">
+        <v>80.15600000000001</v>
+      </c>
+      <c r="AL20">
+        <v>-0.00868499930948019</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:38">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>9.80458894958446</v>
+      </c>
+      <c r="C21">
+        <v>6.24064602414884</v>
+      </c>
+      <c r="D21">
+        <v>2.20172618969779</v>
+      </c>
+      <c r="E21">
+        <v>-0.917449772357941</v>
+      </c>
+      <c r="F21">
+        <v>-0.296844402044544</v>
+      </c>
+      <c r="G21">
+        <v>41.3273940627237</v>
+      </c>
+      <c r="H21">
+        <v>35.5851864870933</v>
+      </c>
+      <c r="I21">
+        <v>38.5296507920009</v>
+      </c>
+      <c r="J21">
+        <v>48.7169187540581</v>
+      </c>
+      <c r="K21">
+        <v>617449991504.4</v>
+      </c>
+      <c r="L21">
         <v>-0.392690505099296</v>
       </c>
-      <c r="C21">
+      <c r="M21">
+        <v>20964.2774847073</v>
+      </c>
+      <c r="N21">
+        <v>10369.5553585271</v>
+      </c>
+      <c r="O21">
+        <v>-1.33462176886584</v>
+      </c>
+      <c r="Q21">
+        <v>-0.306684851646423</v>
+      </c>
+      <c r="R21">
+        <v>11.1079031013032</v>
+      </c>
+      <c r="S21">
+        <v>19.8103353511537</v>
+      </c>
+      <c r="T21">
+        <v>18.5191670625259</v>
+      </c>
+      <c r="U21">
+        <v>38.9323214651119</v>
+      </c>
+      <c r="V21">
         <v>3.63596142127045</v>
       </c>
-      <c r="D21">
+      <c r="W21">
         <v>13.1770157274916</v>
       </c>
-      <c r="E21">
+      <c r="X21">
+        <v>74.53</v>
+      </c>
+      <c r="Y21">
+        <v>0.508905926294583</v>
+      </c>
+      <c r="Z21">
+        <v>-1.61318460276811</v>
+      </c>
+      <c r="AA21">
+        <v>-0.841869175434113</v>
+      </c>
+      <c r="AB21">
+        <v>125762982</v>
+      </c>
+      <c r="AD21">
+        <v>0.0125951962545514</v>
+      </c>
+      <c r="AE21">
+        <v>-0.657918453216553</v>
+      </c>
+      <c r="AF21">
         <v>12.787748609973</v>
       </c>
-      <c r="F21">
+      <c r="AG21">
+        <v>183056094117.556</v>
+      </c>
+      <c r="AH21">
+        <v>3.91541539352767</v>
+      </c>
+      <c r="AI21">
+        <v>77.46197225711281</v>
+      </c>
+      <c r="AJ21">
         <v>3.477</v>
       </c>
+      <c r="AK21">
+        <v>80.444</v>
+      </c>
+      <c r="AL21">
+        <v>0.008570964448153969</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:38">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>9.73369120198331</v>
+      </c>
+      <c r="C22">
+        <v>7.44248480668269</v>
+      </c>
+      <c r="D22">
+        <v>2.56401799892127</v>
+      </c>
+      <c r="E22">
+        <v>-0.921630203723907</v>
+      </c>
+      <c r="F22">
+        <v>2.39690767780379</v>
+      </c>
+      <c r="G22">
+        <v>45.8373464112123</v>
+      </c>
+      <c r="H22">
+        <v>36.932589757811</v>
+      </c>
+      <c r="I22">
+        <v>39.2353720871536</v>
+      </c>
+      <c r="J22">
+        <v>56.8349663757805</v>
+      </c>
+      <c r="K22">
+        <v>616686384395</v>
+      </c>
+      <c r="L22">
         <v>-8.354034565763641</v>
       </c>
-      <c r="C22">
+      <c r="M22">
+        <v>19354.1248722314</v>
+      </c>
+      <c r="N22">
+        <v>8841.270751132801</v>
+      </c>
+      <c r="O22">
+        <v>-9.102871530267979</v>
+      </c>
+      <c r="P22">
+        <v>44.6</v>
+      </c>
+      <c r="Q22">
+        <v>-0.27033868432045</v>
+      </c>
+      <c r="R22">
+        <v>12.1968302771767</v>
+      </c>
+      <c r="S22">
+        <v>21.6980704220947</v>
+      </c>
+      <c r="T22">
+        <v>18.6445328282522</v>
+      </c>
+      <c r="U22">
+        <v>37.6191836120664</v>
+      </c>
+      <c r="V22">
         <v>3.39683415570006</v>
       </c>
-      <c r="D22">
+      <c r="W22">
         <v>13.2763978985871</v>
       </c>
-      <c r="E22">
+      <c r="X22">
+        <v>70.449</v>
+      </c>
+      <c r="Y22">
+        <v>0.717897860988845</v>
+      </c>
+      <c r="Z22">
+        <v>-3.63899768661869</v>
+      </c>
+      <c r="AA22">
+        <v>-0.791455745697021</v>
+      </c>
+      <c r="AB22">
+        <v>126799054</v>
+      </c>
+      <c r="AC22">
+        <v>4.3</v>
+      </c>
+      <c r="AD22">
+        <v>-0.0129100447520614</v>
+      </c>
+      <c r="AE22">
+        <v>-0.642182171344757</v>
+      </c>
+      <c r="AF22">
         <v>13.8975134527584</v>
       </c>
-      <c r="F22">
+      <c r="AG22">
+        <v>199069188921.046</v>
+      </c>
+      <c r="AH22">
+        <v>5.07902828726659</v>
+      </c>
+      <c r="AI22">
+        <v>76.8545556992201</v>
+      </c>
+      <c r="AJ22">
         <v>4.44</v>
       </c>
+      <c r="AK22">
+        <v>80.73099999999999</v>
+      </c>
+      <c r="AL22">
+        <v>-0.0273882187902927</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:38">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>10.8515854374197</v>
+      </c>
+      <c r="C23">
+        <v>7.45681853582088</v>
+      </c>
+      <c r="D23">
+        <v>2.04852607538268</v>
+      </c>
+      <c r="E23">
+        <v>-1.02063989639282</v>
+      </c>
+      <c r="F23">
+        <v>-0.346548814041227</v>
+      </c>
+      <c r="G23">
+        <v>44.8609558048196</v>
+      </c>
+      <c r="H23">
+        <v>35.0570605491873</v>
+      </c>
+      <c r="I23">
+        <v>40.5691931994994</v>
+      </c>
+      <c r="J23">
+        <v>46.8967649892505</v>
+      </c>
+      <c r="K23">
+        <v>601474054897.8</v>
+      </c>
+      <c r="L23">
         <v>6.04848345704632</v>
       </c>
-      <c r="C23">
+      <c r="M23">
+        <v>20782.5877425331</v>
+      </c>
+      <c r="N23">
+        <v>10314.0506725979</v>
+      </c>
+      <c r="O23">
+        <v>5.34306679081725</v>
+      </c>
+      <c r="Q23">
+        <v>-0.3435437977314</v>
+      </c>
+      <c r="R23">
+        <v>11.4047335554869</v>
+      </c>
+      <c r="S23">
+        <v>20.8923836619005</v>
+      </c>
+      <c r="T23">
+        <v>18.3430886480017</v>
+      </c>
+      <c r="U23">
+        <v>42.5001044331777</v>
+      </c>
+      <c r="V23">
         <v>5.68920847683757</v>
       </c>
-      <c r="D23">
+      <c r="W23">
         <v>13.9003389285049</v>
       </c>
-      <c r="E23">
+      <c r="X23">
+        <v>69.75</v>
+      </c>
+      <c r="Y23">
+        <v>0.661419726405739</v>
+      </c>
+      <c r="Z23">
+        <v>-3.32386358575189</v>
+      </c>
+      <c r="AA23">
+        <v>-0.687615871429443</v>
+      </c>
+      <c r="AB23">
+        <v>127648148</v>
+      </c>
+      <c r="AD23">
+        <v>-0.251374453306198</v>
+      </c>
+      <c r="AE23">
+        <v>-0.807996511459351</v>
+      </c>
+      <c r="AF23">
         <v>13.411262121913</v>
       </c>
-      <c r="F23">
+      <c r="AG23">
+        <v>207799490381.042</v>
+      </c>
+      <c r="AH23">
+        <v>4.12398114778684</v>
+      </c>
+      <c r="AI23">
+        <v>83.06929763267711</v>
+      </c>
+      <c r="AJ23">
         <v>4.019</v>
       </c>
+      <c r="AK23">
+        <v>81.01600000000001</v>
+      </c>
+      <c r="AL23">
+        <v>-0.0774139538407326</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:38">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>9.785893749462151</v>
+      </c>
+      <c r="C24">
+        <v>6.92949899538784</v>
+      </c>
+      <c r="D24">
+        <v>2.08482456008448</v>
+      </c>
+      <c r="E24">
+        <v>-1.01208603382111</v>
+      </c>
+      <c r="F24">
+        <v>-1.29019416052739</v>
+      </c>
+      <c r="G24">
+        <v>43.9835270548749</v>
+      </c>
+      <c r="H24">
+        <v>34.2597422077016</v>
+      </c>
+      <c r="I24">
+        <v>42.9460448302063</v>
+      </c>
+      <c r="J24">
+        <v>40.9309512607202</v>
+      </c>
+      <c r="K24">
+        <v>585464239733.2</v>
+      </c>
+      <c r="L24">
         <v>3.71098893117183</v>
       </c>
-      <c r="C24">
+      <c r="M24">
+        <v>23379.7338940539</v>
+      </c>
+      <c r="N24">
+        <v>11402.1410374782</v>
+      </c>
+      <c r="O24">
+        <v>2.93285765177889</v>
+      </c>
+      <c r="P24">
+        <v>43.5</v>
+      </c>
+      <c r="Q24">
+        <v>-0.281723529100418</v>
+      </c>
+      <c r="R24">
+        <v>11.1346118972764</v>
+      </c>
+      <c r="S24">
+        <v>22.3129296276289</v>
+      </c>
+      <c r="T24">
+        <v>19.2773352259497</v>
+      </c>
+      <c r="U24">
+        <v>45.8808899526489</v>
+      </c>
+      <c r="V24">
         <v>7.89627619168551</v>
       </c>
-      <c r="D24">
+      <c r="W24">
         <v>14.8599971692423</v>
       </c>
-      <c r="E24">
+      <c r="X24">
+        <v>73.973</v>
+      </c>
+      <c r="Y24">
+        <v>0.686105132578991</v>
+      </c>
+      <c r="Z24">
+        <v>-4.31072883398904</v>
+      </c>
+      <c r="AA24">
+        <v>-0.689268112182617</v>
+      </c>
+      <c r="AB24">
+        <v>128613117</v>
+      </c>
+      <c r="AC24">
+        <v>2.3</v>
+      </c>
+      <c r="AD24">
+        <v>-0.148309499025345</v>
+      </c>
+      <c r="AE24">
+        <v>-0.8694250583648681</v>
+      </c>
+      <c r="AF24">
         <v>13.408403759922</v>
       </c>
-      <c r="F24">
+      <c r="AG24">
+        <v>201118689946.087</v>
+      </c>
+      <c r="AH24">
+        <v>3.32190681281323</v>
+      </c>
+      <c r="AI24">
+        <v>88.8269347828552</v>
+      </c>
+      <c r="AJ24">
         <v>3.256</v>
       </c>
+      <c r="AK24">
+        <v>81.3</v>
+      </c>
+      <c r="AL24">
+        <v>-0.119756743311882</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:38">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
+        <v>10.2387496913746</v>
+      </c>
+      <c r="C25">
+        <v>7.15119110000245</v>
+      </c>
+      <c r="D25">
+        <v>2.07732748969619</v>
+      </c>
+      <c r="E25">
+        <v>-1.02057874202728</v>
+      </c>
+      <c r="F25">
+        <v>-0.702155201258809</v>
+      </c>
+      <c r="G25">
+        <v>45.1431938521023</v>
+      </c>
+      <c r="H25">
+        <v>33.2369362044555</v>
+      </c>
+      <c r="I25">
+        <v>36.1666703433344</v>
+      </c>
+      <c r="J25">
+        <v>34.1601439110051</v>
+      </c>
+      <c r="K25">
+        <v>595917670218</v>
+      </c>
+      <c r="L25">
         <v>3.2953909570288</v>
       </c>
-      <c r="C25">
+      <c r="M25">
+        <v>24854.5822142309</v>
+      </c>
+      <c r="N25">
+        <v>13826.1306570122</v>
+      </c>
+      <c r="O25">
+        <v>2.39838816655337</v>
+      </c>
+      <c r="Q25">
+        <v>-0.198361441493034</v>
+      </c>
+      <c r="R25">
+        <v>11.1011755462719</v>
+      </c>
+      <c r="S25">
+        <v>22.4670700946052</v>
+      </c>
+      <c r="T25">
+        <v>19.0929739699628</v>
+      </c>
+      <c r="U25">
+        <v>37.6028627773981</v>
+      </c>
+      <c r="V25">
         <v>5.52796087314385</v>
       </c>
-      <c r="D25">
+      <c r="W25">
         <v>15.7675933805407</v>
       </c>
-      <c r="E25">
+      <c r="X25">
+        <v>75.069</v>
+      </c>
+      <c r="Y25">
+        <v>0.656934513100098</v>
+      </c>
+      <c r="Z25">
+        <v>-4.19627848803267</v>
+      </c>
+      <c r="AA25">
+        <v>-0.630761027336121</v>
+      </c>
+      <c r="AB25">
+        <v>129739759</v>
+      </c>
+      <c r="AD25">
+        <v>-0.171988308429718</v>
+      </c>
+      <c r="AE25">
+        <v>-0.806393921375275</v>
+      </c>
+      <c r="AF25">
         <v>14.2293414351689</v>
       </c>
-      <c r="F25">
+      <c r="AG25">
+        <v>214316827085.02</v>
+      </c>
+      <c r="AH25">
+        <v>3.44254738885753</v>
+      </c>
+      <c r="AI25">
+        <v>73.7695331207325</v>
+      </c>
+      <c r="AJ25">
         <v>2.765</v>
       </c>
+      <c r="AK25">
+        <v>81.58199999999999</v>
+      </c>
+      <c r="AL25">
+        <v>-0.115086063742638</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:38">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="C26">
+        <v>7.47042367039987</v>
+      </c>
+      <c r="F26">
+        <v>-0.9035457782812339</v>
+      </c>
+      <c r="H26">
+        <v>34.6539050825782</v>
+      </c>
+      <c r="I26">
+        <v>36.7857440701926</v>
+      </c>
+      <c r="L26">
         <v>1.4540624784799</v>
       </c>
-      <c r="C26">
+      <c r="M26">
+        <v>25688.0964960445</v>
+      </c>
+      <c r="N26">
+        <v>14157.9445835849</v>
+      </c>
+      <c r="O26">
+        <v>0.584780121162638</v>
+      </c>
+      <c r="R26">
+        <v>11.174533115525</v>
+      </c>
+      <c r="U26">
+        <v>37.9258515356765</v>
+      </c>
+      <c r="V26">
         <v>4.72225588452935</v>
       </c>
-      <c r="F26">
+      <c r="AB26">
+        <v>130861007</v>
+      </c>
+      <c r="AG26">
+        <v>232035392464.815</v>
+      </c>
+      <c r="AH26">
+        <v>3.5473573038805</v>
+      </c>
+      <c r="AI26">
+        <v>74.71159560586911</v>
+      </c>
+      <c r="AJ26">
         <v>2.711</v>
+      </c>
+      <c r="AK26">
+        <v>81.86199999999999</v>
       </c>
     </row>
   </sheetData>
